--- a/output/KRT_оптимизация_результат.xlsx
+++ b/output/KRT_оптимизация_результат.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -535,37 +535,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14.1; 13.2; 12.1</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2 + 14.1 + 13.2 + 12.1</t>
+          <t>1.2 + 16.3</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.082141</v>
+        <v>1.092692</v>
       </c>
       <c r="H4" t="n">
-        <v>43.9</v>
+        <v>44.2</v>
       </c>
       <c r="I4" t="n">
-        <v>14220</v>
+        <v>2104</v>
       </c>
       <c r="J4" t="n">
-        <v>192863</v>
+        <v>146950</v>
       </c>
       <c r="K4" t="n">
-        <v>28529</v>
+        <v>24300</v>
       </c>
       <c r="L4" t="n">
-        <v>470345</v>
+        <v>424432</v>
       </c>
       <c r="M4" t="n">
-        <v>47228</v>
+        <v>42999</v>
       </c>
     </row>
     <row r="5">
@@ -584,37 +584,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.2; 20.4; 16.3</t>
+          <t>25.1; 18.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.2 + 17.2 + 20.4 + 16.3</t>
+          <t>11.2 + 25.1 + 18.4</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>1.006719</v>
+        <v>1.004917</v>
       </c>
       <c r="H5" t="n">
-        <v>44.5</v>
+        <v>42.3</v>
       </c>
       <c r="I5" t="n">
-        <v>9262</v>
+        <v>2545</v>
       </c>
       <c r="J5" t="n">
-        <v>203876</v>
+        <v>131644</v>
       </c>
       <c r="K5" t="n">
-        <v>34236</v>
+        <v>13204</v>
       </c>
       <c r="L5" t="n">
-        <v>382521</v>
+        <v>310289</v>
       </c>
       <c r="M5" t="n">
-        <v>58792</v>
+        <v>37760</v>
       </c>
     </row>
     <row r="6">
@@ -633,37 +633,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14.2; 21.3; 21.2</t>
+          <t>28.1; 27.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.2 + 14.2 + 21.3 + 21.2</t>
+          <t>12.2 + 28.1 + 27.2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>1.001689</v>
+        <v>1.110135</v>
       </c>
       <c r="H6" t="n">
-        <v>43.8</v>
+        <v>44.6</v>
       </c>
       <c r="I6" t="n">
-        <v>7976</v>
+        <v>5121</v>
       </c>
       <c r="J6" t="n">
-        <v>406449</v>
+        <v>94175</v>
       </c>
       <c r="K6" t="n">
-        <v>104819</v>
+        <v>57363</v>
       </c>
       <c r="L6" t="n">
-        <v>497616</v>
+        <v>185342</v>
       </c>
       <c r="M6" t="n">
-        <v>114925</v>
+        <v>67469</v>
       </c>
     </row>
     <row r="7">
@@ -682,37 +682,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.2; 1.1; 34.3</t>
+          <t>13.2; 34.1; 35.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.3 + 9.2 + 1.1 + 34.3</t>
+          <t>13.3 + 13.2 + 34.1 + 35.2</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.147663</v>
+        <v>1.01236</v>
       </c>
       <c r="H7" t="n">
-        <v>44.5</v>
+        <v>39.4</v>
       </c>
       <c r="I7" t="n">
-        <v>4725</v>
+        <v>14829</v>
       </c>
       <c r="J7" t="n">
-        <v>326964</v>
+        <v>199917</v>
       </c>
       <c r="K7" t="n">
-        <v>66897</v>
+        <v>38174</v>
       </c>
       <c r="L7" t="n">
-        <v>493641</v>
+        <v>366594</v>
       </c>
       <c r="M7" t="n">
-        <v>75775</v>
+        <v>47052</v>
       </c>
     </row>
     <row r="8">
@@ -731,37 +731,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32.2; 31.2; 24.1</t>
+          <t>14.2; 14.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.3 + 32.2 + 31.2 + 24.1</t>
+          <t>14.3 + 14.2 + 14.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>1.161267</v>
+        <v>1.174036</v>
       </c>
       <c r="H8" t="n">
-        <v>45</v>
+        <v>38.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10087</v>
+        <v>364</v>
       </c>
       <c r="J8" t="n">
-        <v>363093</v>
+        <v>361247</v>
       </c>
       <c r="K8" t="n">
-        <v>59109</v>
+        <v>116982</v>
       </c>
       <c r="L8" t="n">
-        <v>476571</v>
+        <v>474725</v>
       </c>
       <c r="M8" t="n">
-        <v>65330</v>
+        <v>123203</v>
       </c>
     </row>
     <row r="9">
@@ -780,37 +780,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1; 28.1; 27.4</t>
+          <t>33.1; 1.1; 20.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16.2 + 8.1 + 28.1 + 27.4</t>
+          <t>16.2 + 33.1 + 1.1 + 20.4</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>1.021448</v>
+        <v>1.025766</v>
       </c>
       <c r="H9" t="n">
-        <v>43.5</v>
+        <v>44.4</v>
       </c>
       <c r="I9" t="n">
-        <v>6130</v>
+        <v>12658</v>
       </c>
       <c r="J9" t="n">
-        <v>124225</v>
+        <v>411473</v>
       </c>
       <c r="K9" t="n">
-        <v>61252</v>
+        <v>114850</v>
       </c>
       <c r="L9" t="n">
-        <v>157865</v>
+        <v>445113</v>
       </c>
       <c r="M9" t="n">
-        <v>77938</v>
+        <v>131536</v>
       </c>
     </row>
     <row r="10">
@@ -829,37 +829,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.1; 33.1; 35.3</t>
+          <t>15.3; 24.2; 12.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17.3 + 13.1 + 33.1 + 35.3</t>
+          <t>17.3 + 15.3 + 24.2 + 12.1</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.068058</v>
+        <v>1.010633</v>
       </c>
       <c r="H10" t="n">
-        <v>44.8</v>
+        <v>37.9</v>
       </c>
       <c r="I10" t="n">
-        <v>6740</v>
+        <v>7765</v>
       </c>
       <c r="J10" t="n">
-        <v>247727</v>
+        <v>146556</v>
       </c>
       <c r="K10" t="n">
-        <v>63382</v>
+        <v>19347</v>
       </c>
       <c r="L10" t="n">
-        <v>370845</v>
+        <v>269674</v>
       </c>
       <c r="M10" t="n">
-        <v>76730</v>
+        <v>32695</v>
       </c>
     </row>
     <row r="11">
@@ -878,37 +878,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23.2; 31.1; 27.2</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.1 + 23.2 + 31.1 + 27.2</t>
+          <t>2.1 + 35.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.014422</v>
+        <v>1.025213</v>
       </c>
       <c r="H11" t="n">
-        <v>45</v>
+        <v>42.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3001</v>
+        <v>617</v>
       </c>
       <c r="J11" t="n">
-        <v>55029</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>13530</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>382615</v>
+        <v>327586</v>
       </c>
       <c r="M11" t="n">
-        <v>45151</v>
+        <v>31621</v>
       </c>
     </row>
     <row r="12">
@@ -927,37 +927,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23.1; 17.1; 18.3</t>
+          <t>23.1; 32.2; 18.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.2 + 23.1 + 17.1 + 18.3</t>
+          <t>2.2 + 23.1 + 32.2 + 18.3</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>1.003674</v>
+        <v>1.001203</v>
       </c>
       <c r="H12" t="n">
-        <v>43</v>
+        <v>39.9</v>
       </c>
       <c r="I12" t="n">
-        <v>13208</v>
+        <v>12915</v>
       </c>
       <c r="J12" t="n">
-        <v>156110</v>
+        <v>96803</v>
       </c>
       <c r="K12" t="n">
-        <v>8340</v>
+        <v>902</v>
       </c>
       <c r="L12" t="n">
-        <v>392643</v>
+        <v>333336</v>
       </c>
       <c r="M12" t="n">
-        <v>12785</v>
+        <v>5347</v>
       </c>
     </row>
     <row r="13">
@@ -976,37 +976,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25.1; 8.2</t>
+          <t>23.2; 13.1; 31.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20.1 + 25.1 + 8.2</t>
+          <t>20.1 + 23.2 + 13.1 + 31.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>1.014622</v>
+        <v>1.000965</v>
       </c>
       <c r="H13" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3158</v>
+        <v>7053</v>
       </c>
       <c r="J13" t="n">
-        <v>43708</v>
+        <v>111469</v>
       </c>
       <c r="K13" t="n">
-        <v>5292</v>
+        <v>17293</v>
       </c>
       <c r="L13" t="n">
-        <v>158374</v>
+        <v>226135</v>
       </c>
       <c r="M13" t="n">
-        <v>39330</v>
+        <v>51331</v>
       </c>
     </row>
     <row r="14">
@@ -1025,37 +1025,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.3; 15.1; 18.4</t>
+          <t>18.1; 19.1; 27.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.1 + 15.3 + 15.1 + 18.4</t>
+          <t>22.1 + 18.1 + 19.1 + 27.4</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>1.002013</v>
+        <v>1.007459</v>
       </c>
       <c r="H14" t="n">
-        <v>44.7</v>
+        <v>36.6</v>
       </c>
       <c r="I14" t="n">
-        <v>1405</v>
+        <v>6120</v>
       </c>
       <c r="J14" t="n">
-        <v>208522</v>
+        <v>155135</v>
       </c>
       <c r="K14" t="n">
-        <v>81156</v>
+        <v>12473</v>
       </c>
       <c r="L14" t="n">
-        <v>332792</v>
+        <v>279405</v>
       </c>
       <c r="M14" t="n">
-        <v>93261</v>
+        <v>24578</v>
       </c>
     </row>
     <row r="15">
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24.2; 18.1; 11.1</t>
+          <t>17.1; 8.2; 21.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.1 + 24.2 + 18.1 + 11.1</t>
+          <t>24.1 + 17.1 + 8.2 + 21.3</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>1.009709</v>
+        <v>1.000541</v>
       </c>
       <c r="H15" t="n">
-        <v>44.7</v>
+        <v>44.4</v>
       </c>
       <c r="I15" t="n">
-        <v>11469</v>
+        <v>9693</v>
       </c>
       <c r="J15" t="n">
-        <v>271868</v>
+        <v>77735</v>
       </c>
       <c r="K15" t="n">
-        <v>53259</v>
+        <v>7730</v>
       </c>
       <c r="L15" t="n">
-        <v>327271</v>
+        <v>420032</v>
       </c>
       <c r="M15" t="n">
-        <v>70837</v>
+        <v>66601</v>
       </c>
     </row>
     <row r="16">
@@ -1118,42 +1118,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18.2; 34.1</t>
+          <t>8.1; 15.1; 11.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.3 + 18.2 + 34.1</t>
+          <t>29.1 + 8.1 + 15.1 + 11.1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>1.026733</v>
+        <v>1.041414</v>
       </c>
       <c r="H16" t="n">
-        <v>45</v>
+        <v>40.3</v>
       </c>
       <c r="I16" t="n">
-        <v>163</v>
+        <v>1218</v>
       </c>
       <c r="J16" t="n">
-        <v>158654</v>
+        <v>280591</v>
       </c>
       <c r="K16" t="n">
-        <v>31313</v>
+        <v>119118</v>
       </c>
       <c r="L16" t="n">
-        <v>501241</v>
+        <v>335994</v>
       </c>
       <c r="M16" t="n">
-        <v>54704</v>
+        <v>136696</v>
       </c>
     </row>
     <row r="17">
@@ -1167,42 +1167,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.3; 35.2</t>
+          <t>18.2; 17.2; 21.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.1 + 20.3 + 35.2</t>
+          <t>31.3 + 18.2 + 17.2 + 21.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>1.181556</v>
+        <v>1.024556</v>
       </c>
       <c r="H17" t="n">
-        <v>45</v>
+        <v>41.7</v>
       </c>
       <c r="I17" t="n">
-        <v>3181</v>
+        <v>163</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>174185</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>9936</v>
       </c>
       <c r="L17" t="n">
-        <v>375469</v>
+        <v>516772</v>
       </c>
       <c r="M17" t="n">
-        <v>53070</v>
+        <v>33327</v>
       </c>
     </row>
     <row r="18">
@@ -1216,42 +1216,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>19.1; 30.3</t>
+          <t>31.2; 20.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7.2 + 19.1 + 30.3</t>
+          <t>7.1 + 31.2 + 20.3</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>1.009036</v>
+        <v>1.239584</v>
       </c>
       <c r="H18" t="n">
-        <v>44.6</v>
+        <v>43.3</v>
       </c>
       <c r="I18" t="n">
-        <v>111</v>
+        <v>1837</v>
       </c>
       <c r="J18" t="n">
-        <v>110173</v>
+        <v>10394</v>
       </c>
       <c r="K18" t="n">
-        <v>11408</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>335788</v>
+        <v>385863</v>
       </c>
       <c r="M18" t="n">
-        <v>39498</v>
+        <v>53070</v>
       </c>
     </row>
     <row r="19">
@@ -1265,42 +1265,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>32.3; 25.2</t>
+          <t>9.2; 30.3; 34.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9.1 + 32.3 + 25.2</t>
+          <t>7.2 + 9.2 + 30.3 + 34.3</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>1.045867</v>
+        <v>1.024566</v>
       </c>
       <c r="H19" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="I19" t="n">
-        <v>11300</v>
+        <v>558</v>
       </c>
       <c r="J19" t="n">
-        <v>20748</v>
+        <v>128690</v>
       </c>
       <c r="K19" t="n">
-        <v>615</v>
+        <v>11979</v>
       </c>
       <c r="L19" t="n">
-        <v>166133</v>
+        <v>354305</v>
       </c>
       <c r="M19" t="n">
-        <v>13604</v>
+        <v>40069</v>
       </c>
     </row>
     <row r="20">
@@ -1309,47 +1309,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Самостоятельная &gt;45 га</t>
+          <t>Комбинация</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32.3; 25.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.1 + 32.3 + 25.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>1.21</v>
+        <v>1.045867</v>
       </c>
       <c r="H20" t="n">
-        <v>71.40000000000001</v>
+        <v>45</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>11300</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>20748</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="L20" t="n">
-        <v>570058</v>
+        <v>166133</v>
       </c>
       <c r="M20" t="n">
-        <v>116631</v>
+        <v>13604</v>
       </c>
     </row>
     <row r="21">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="H21" t="n">
-        <v>47.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>452216</v>
+        <v>570058</v>
       </c>
       <c r="M21" t="n">
-        <v>89329</v>
+        <v>116631</v>
       </c>
     </row>
     <row r="22">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="H22" t="n">
-        <v>119.8</v>
+        <v>47.4</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1444,10 +1444,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>829416</v>
+        <v>452216</v>
       </c>
       <c r="M22" t="n">
-        <v>101981</v>
+        <v>89329</v>
       </c>
     </row>
     <row r="23">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="H23" t="n">
-        <v>83.59999999999999</v>
+        <v>119.8</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1493,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>306299</v>
+        <v>829416</v>
       </c>
       <c r="M23" t="n">
-        <v>30483</v>
+        <v>101981</v>
       </c>
     </row>
     <row r="24">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="H24" t="n">
-        <v>87.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1542,10 +1542,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>414459</v>
+        <v>306299</v>
       </c>
       <c r="M24" t="n">
-        <v>106733</v>
+        <v>30483</v>
       </c>
     </row>
     <row r="25">
@@ -1569,17 +1569,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="H25" t="n">
-        <v>52.6</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>125573</v>
+        <v>414459</v>
       </c>
       <c r="M25" t="n">
-        <v>27756</v>
+        <v>106733</v>
       </c>
     </row>
     <row r="26">
@@ -1618,17 +1618,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="H26" t="n">
-        <v>173.4</v>
+        <v>52.6</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1640,10 +1640,10 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1130648</v>
+        <v>125573</v>
       </c>
       <c r="M26" t="n">
-        <v>62674</v>
+        <v>27756</v>
       </c>
     </row>
     <row r="27">
@@ -1667,17 +1667,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="H27" t="n">
-        <v>98.59999999999999</v>
+        <v>173.4</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1689,10 +1689,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>255062</v>
+        <v>1130648</v>
       </c>
       <c r="M27" t="n">
-        <v>96838</v>
+        <v>62674</v>
       </c>
     </row>
     <row r="28">
@@ -1716,46 +1716,95 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H28" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>255062</v>
+      </c>
+      <c r="M28" t="n">
+        <v>96838</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Самостоятельная &gt;45 га</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
         <v>1.02</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H29" t="n">
         <v>62.1</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>409090</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Итого уникальных площадок: 68 из 80 (85%)</t>
-        </is>
-      </c>
-    </row>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Обычных комбинаций: 16; крупных самостоятельных площадок: 9</t>
+          <t>Итого уникальных площадок: 68 из 80 (85%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Обычных комбинаций: 17; крупных самостоятельных площадок: 9</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2303,7 +2352,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>106136</v>
+        <v>96860</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -2323,7 +2372,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2890009</v>
+        <v>2547712</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -2343,7 +2392,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>623137</v>
+        <v>564266</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -2486,7 +2535,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Количество обычных комбинаций / крупных площадок = 16 / 9 (эталон: 16 / 9)</t>
+          <t>Количество обычных комбинаций / крупных площадок = 17 / 9 (эталон: 17 / 9)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2520,212 +2569,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Найден АЛЬТЕРНАТИВНЫЙ ЭКВИВАЛЕНТНЫЙ ОПТИМУМ: все шесть целевых значений лексикографической оптимизации совпадают с эталоном (охват, компактность, суммы трёх предельных эффектов), но конкретная группировка площадок по комбинациям отличается.</t>
+          <t>Состав итогового набора ПОЛНОСТЬЮ совпадает с эталоном: те же 68 площадок и та же разбивка по опорным площадкам (каждая обычная комбинация содержит тот же набор дополнительных площадок, что и в методике).</t>
         </is>
       </c>
       <c r="B18" s="3" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Это возможно потому, что лексикографические цели фиксируют только суммарные показатели по всем комбинациям, а не то, какая именно дополнительная площадка досталась какой опорной — при равных суммах решатель вправе вернуть любую из существующих равнозначных группировок.</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Набор из 68 площадок при этом идентичен эталону — отличается только распределение по опорным.</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Изменившиеся комбинации:</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 1.2: эталон [16.3, 35.3] -&gt; новое решение [12.1, 13.2, 14.1]</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 11.2: эталон [11.1, 12.1, 35.2] -&gt; новое решение [16.3, 17.2, 20.4]</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 12.2: эталон [28.1, 30.3] -&gt; новое решение [14.2, 21.2, 21.3]</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 13.3: эталон [15.1, 20.4, 24.2] -&gt; новое решение [1.1, 34.3, 9.2]</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 14.3: эталон [14.2, 18.2, 21.3] -&gt; новое решение [24.1, 31.2, 32.2]</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 16.2: эталон [13.2, 20.3, 24.1] -&gt; новое решение [27.4, 28.1, 8.1]</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 17.3: эталон [17.2, 33.1, 8.2] -&gt; новое решение [13.1, 33.1, 35.3]</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 2.1: эталон [23.2, 34.3, 8.1] -&gt; новое решение [23.2, 27.2, 31.1]</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 2.2: эталон [14.1, 18.3, 23.1] -&gt; новое решение [17.1, 18.3, 23.1]</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 20.1: эталон [13.1, 17.1, 31.2] -&gt; новое решение [25.1, 8.2]</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 22.1: эталон [18.4, 21.2, 9.2] -&gt; новое решение [15.1, 15.3, 18.4]</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 29.1: эталон [1.1, 19.1, 25.1] -&gt; новое решение [11.1, 18.1, 24.2]</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 31.3: эталон [15.3, 32.2, 34.1] -&gt; новое решение [18.2, 34.1]</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 7.1: эталон [27.4] -&gt; новое решение [20.3, 35.2]</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 7.2: эталон [18.1, 25.2, 31.1] -&gt; новое решение [19.1, 30.3]</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    опорная 9.1: эталон [27.2, 32.3] -&gt; новое решение [25.2, 32.3]</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Это математически допустимая ситуация (см. раздел 6.7 промпта) — не считается ошибкой.</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
